--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -36,99 +36,99 @@
     <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
+    <t xml:space="preserve">Teodoro Schmidt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Galvarino</t>
   </si>
   <si>
+    <t xml:space="preserve">Freire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitrufquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loncoche</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cholchol</t>
   </si>
   <si>
-    <t xml:space="preserve">Renaico</t>
+    <t xml:space="preserve">Vilcún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perquenco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipeuco</t>
   </si>
   <si>
     <t xml:space="preserve">Pucón</t>
   </si>
   <si>
-    <t xml:space="preserve">Vilcún</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villarrica</t>
   </si>
   <si>
-    <t xml:space="preserve">Teodoro Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loncoche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipeuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pitrufquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perquenco</t>
+    <t xml:space="preserve">Curacautín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collipulli</t>
   </si>
   <si>
     <t xml:space="preserve">Saavedra</t>
   </si>
   <si>
+    <t xml:space="preserve">Carahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lautaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toltén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traiguén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curarrehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Imperial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
-    <t xml:space="preserve">Curacautín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toltén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purén</t>
+    <t xml:space="preserve">Victoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
     <t xml:space="preserve">Lonquimay</t>
   </si>
   <si>
-    <t xml:space="preserve">Curarrehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lautaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Imperial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiguén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria</t>
+    <t xml:space="preserve">Angol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temuco</t>
   </si>
   <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Temuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,13 +571,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9106</v>
+        <v>9117</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13.91</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="3">
@@ -588,13 +588,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9121</v>
+        <v>9106</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.26</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="4">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9209</v>
+        <v>9105</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12.97</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="5">
@@ -622,13 +622,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9115</v>
+        <v>9209</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12.72</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9119</v>
+        <v>9114</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11.14</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9120</v>
+        <v>9109</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10.59</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="8">
@@ -673,13 +673,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>9117</v>
+        <v>9121</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9.8</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="9">
@@ -690,13 +690,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>9109</v>
+        <v>9119</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8.61</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="10">
@@ -707,13 +707,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9110</v>
+        <v>9113</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.18</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="11">
@@ -724,13 +724,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>9114</v>
+        <v>9110</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.12</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="12">
@@ -741,13 +741,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>9113</v>
+        <v>9115</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7.72</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="13">
@@ -758,13 +758,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9116</v>
+        <v>9120</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7.45</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="14">
@@ -775,13 +775,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9103</v>
+        <v>9203</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7.09</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="15">
@@ -792,13 +792,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9203</v>
+        <v>9208</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7.09</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="16">
@@ -809,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>9105</v>
+        <v>9202</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6.8</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="17">
@@ -826,13 +826,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9118</v>
+        <v>9116</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5.44</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="18">
@@ -843,13 +843,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9208</v>
+        <v>9102</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5.44</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="19">
@@ -860,13 +860,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9205</v>
+        <v>9108</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5.05</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="20">
@@ -877,13 +877,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>9104</v>
+        <v>9118</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.97</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="21">
@@ -894,13 +894,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9108</v>
+        <v>9112</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3.98</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="22">
@@ -911,13 +911,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9111</v>
+        <v>9210</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3.4</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="23">
@@ -928,13 +928,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9206</v>
+        <v>9104</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3.14</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9102</v>
+        <v>9111</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2.76</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="25">
@@ -962,13 +962,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9202</v>
+        <v>9103</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="26">
@@ -979,13 +979,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>9112</v>
+        <v>9211</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="27">
@@ -996,13 +996,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>9207</v>
+        <v>9206</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2.08</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="28">
@@ -1013,13 +1013,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>9210</v>
+        <v>9207</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.51</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="29">
@@ -1030,13 +1030,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>9211</v>
+        <v>9205</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
@@ -1047,13 +1047,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9204</v>
+        <v>9201</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="32">
@@ -1081,13 +1081,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>9201</v>
+        <v>9204</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-1.28</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-2.21</v>
+        <v>-3.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.41</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="3">
@@ -594,7 +594,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.14</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.85</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.83</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.78</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.66</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +679,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.47</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.46</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.41</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="11">
@@ -730,7 +730,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.15</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.99</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.87</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.83</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="15">
@@ -798,7 +798,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.81</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.63</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="17">
@@ -832,7 +832,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.36</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.26</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="19">
@@ -866,7 +866,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.22</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.17</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="21">
@@ -900,7 +900,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.15</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="22">
@@ -917,7 +917,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.94</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="23">
@@ -934,7 +934,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.85</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="24">
@@ -951,7 +951,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.81</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="25">
@@ -968,7 +968,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.74</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="26">
@@ -985,7 +985,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.49</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="27">
@@ -1002,7 +1002,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.45</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="28">
@@ -1019,7 +1019,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.36</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="29">
@@ -1036,7 +1036,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.08</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="30">
@@ -1053,7 +1053,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.07</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="31">
@@ -1070,7 +1070,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.56</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="32">
@@ -1087,7 +1087,7 @@
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-1.85</v>
+        <v>-18.47</v>
       </c>
     </row>
     <row r="33">
@@ -1104,7 +1104,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-3.59</v>
+        <v>-35.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:28</t>
+    <t xml:space="preserve">2026-10-05 08:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
